--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260502_203021.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260502_203021.xlsx
@@ -6202,7 +6202,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260502_203021.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260502_203021.xlsx
@@ -6202,7 +6202,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
